--- a/out/MLP_Base_repeat_5_000008.xlsx
+++ b/out/MLP_Base_repeat_5_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.305762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001662794399412815</v>
+        <v>-0.0001400802099283319</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1910231395823393</v>
+        <v>-0.1609252563232461</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1913295839891509</v>
+        <v>-0.1611864152315984</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5040010428644206</v>
+        <v>0.4353711682502186</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8176407166767614</v>
+        <v>0.7103923643335108</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03591000507235205</v>
+        <v>0.03102010432907314</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3846506966477283</v>
+        <v>0.3363625806186774</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06297391359999649</v>
+        <v>0.05439882210839907</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4746765347728047</v>
+        <v>0.4141296951803143</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07650555607728514</v>
+        <v>0.06608814441179658</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5647083654748106</v>
+        <v>0.4919019858187302</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02024545201290989</v>
+        <v>0.01748841384980207</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5285954117157299</v>
+        <v>0.4607066224258325</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01124771549037149</v>
+        <v>0.009715655634874901</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.305762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5308259660250421</v>
+        <v>0.4626327737459778</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02363135427030356</v>
+        <v>0.02041393983913546</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.566857143400217</v>
+        <v>0.4937572820178666</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009281512551243565</v>
+        <v>0.00801715168745923</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5617671660148119</v>
+        <v>0.4893599112037255</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006608401308254594</v>
+        <v>0.00570798516769411</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5656991011666167</v>
+        <v>0.4927553872779843</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002598077428187005</v>
+        <v>0.002243667825288305</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.564281340156882</v>
+        <v>0.4915302914631194</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001473215227162081</v>
+        <v>0.00127129010228384</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5646268176669809</v>
+        <v>0.4918278935260622</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005575228614965449</v>
+        <v>0.0004811888615022328</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5642686416092328</v>
+        <v>0.4915179608555997</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002592305064198813</v>
+        <v>0.0002228988117871476</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5642280044223773</v>
+        <v>0.4914822237819368</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.187903532247694e-05</v>
+        <v>7.815450531845937e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.564152310334987</v>
+        <v>0.4914162507023255</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.361914509954013e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5641075772852958</v>
+        <v>0.4913768153925931</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5641025549460349</v>
+        <v>0.4913717960319002</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.564098645569686</v>
+        <v>0.4913677412390646</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5640963946419545</v>
+        <v>0.4913651238356458</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5640908029819461</v>
+        <v>0.4913596065936561</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5640844789879382</v>
+        <v>0.4913532825996482</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5640791111993598</v>
+        <v>0.4913479148110698</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5640791479478515</v>
+        <v>0.4913479515595615</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5640792581933272</v>
+        <v>0.4913480618050371</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5640793316903108</v>
+        <v>0.4913481353020207</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5640795154327699</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5640810588694264</v>
+        <v>0.4913498624811363</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5640825288090995</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5640837782578214</v>
+        <v>0.4913525818695314</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5640851379520188</v>
+        <v>0.4913539415637287</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5640829330425094</v>
+        <v>0.4913517366542194</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5640825288090995</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5640822348211647</v>
+        <v>0.4913510384328747</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5640819040847384</v>
+        <v>0.4913507076964483</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5640816100968039</v>
+        <v>0.4913504137085138</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5640812426118855</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.56408113236641</v>
+        <v>0.4913499359781199</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5640810956179183</v>
+        <v>0.4913498992296282</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5640812426118855</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5640807648814919</v>
+        <v>0.4913495684932019</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5640817203422792</v>
+        <v>0.4913505239539891</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5640813528573611</v>
+        <v>0.491350156469071</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.564081793839263</v>
+        <v>0.491350597450973</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5640811691149019</v>
+        <v>0.4913499727266119</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5640809853724428</v>
+        <v>0.4913497889841527</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5640805811390327</v>
+        <v>0.4913493847507427</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5640797359237207</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.564079699175229</v>
+        <v>0.491348502786939</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5640798461691963</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5640797726722127</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.905762781659078</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5640798461691963</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5640798829176882</v>
+        <v>0.4913486865293982</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5640797726722127</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5640802136541146</v>
+        <v>0.4913490172658246</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5640801034086391</v>
+        <v>0.4913489070203491</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5640800666601472</v>
+        <v>0.4913488702718571</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5640799931631636</v>
+        <v>0.4913487967748735</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5640799564146719</v>
+        <v>0.4913487600263818</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5640797359237207</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5640796624267371</v>
+        <v>0.4913484660384471</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5640795889297535</v>
+        <v>0.4913483925414635</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5640796256782454</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5640795154327699</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5640796256782454</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.905762781659078</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5640799196661799</v>
+        <v>0.4913487232778899</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000008.xlsx
+++ b/out/MLP_Base_repeat_5_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.5955144575003584</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001662794399412815</v>
+        <v>-0.0001268986134462757</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1910231395823393</v>
+        <v>-0.1457821337244151</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1911894190222806</v>
+        <v>-0.1459090323378613</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1913295839891509</v>
+        <v>-0.1460198482380828</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5040010428644206</v>
+        <v>0.3984684831700167</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8176407166767614</v>
+        <v>0.6516827066599384</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03591000507235205</v>
+        <v>0.02839079576504601</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3846506966477283</v>
+        <v>0.3093561868546149</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06297391359999649</v>
+        <v>0.04978778242834846</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4746765347728047</v>
+        <v>0.3805316650209108</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07650555607728514</v>
+        <v>0.06048658754653359</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5647083654748106</v>
+        <v>0.4517120636879264</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02024545201290989</v>
+        <v>0.01600626656819838</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5285954117157299</v>
+        <v>0.4231607839207831</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01124771549037149</v>
+        <v>0.00889165984094642</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5308259660250421</v>
+        <v>0.4249232363480751</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02363135427030356</v>
+        <v>0.01868350094727638</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.566857143400217</v>
+        <v>0.4534093974891268</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009281512551243565</v>
+        <v>0.007336528310594483</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5617671660148119</v>
+        <v>0.4493843578343242</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006608401308254594</v>
+        <v>0.005223278394710401</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5656991011666167</v>
+        <v>0.4524918418123275</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002598077428187005</v>
+        <v>0.002053563057449922</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.905762781659078</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.564281340156882</v>
+        <v>0.4513698941943718</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001473215227162081</v>
+        <v>0.001163391180593178</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5646268176669809</v>
+        <v>0.4516419139573071</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005575228614965449</v>
+        <v>0.0004400859384283726</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5642686416092328</v>
+        <v>0.4513577606188883</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002592305064198813</v>
+        <v>0.0002030815238056566</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5642280044223773</v>
+        <v>0.4513246228372562</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.187903532247694e-05</v>
+        <v>7.169590296362756e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.564152310334987</v>
+        <v>0.4512636566847388</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.361914509954013e-05</v>
+        <v>1.741833032797311e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5641075772852958</v>
+        <v>0.4512272017260541</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5641025549460349</v>
+        <v>0.4512221838546451</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.564098645569686</v>
+        <v>0.4512180563535662</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5640963946419545</v>
+        <v>0.4512152552076886</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5640908029819461</v>
+        <v>0.4512098114626822</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5640844789879382</v>
+        <v>0.4512038187292519</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5640791111993598</v>
+        <v>0.4511984509406735</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5640791479478515</v>
+        <v>0.4511984876891652</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5640792581933272</v>
+        <v>0.4511985979346407</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5640793316903108</v>
+        <v>0.4511986714316243</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5640795154327699</v>
+        <v>0.4511988551740835</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5640810588694264</v>
+        <v>0.45120039861074</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5640825288090995</v>
+        <v>0.4512018685504131</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5640837782578214</v>
+        <v>0.451203117999135</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5640851379520188</v>
+        <v>0.4512044776933324</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5640829330425094</v>
+        <v>0.4512022727838231</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5640825288090995</v>
+        <v>0.4512018685504131</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4512010233351011</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5640822348211647</v>
+        <v>0.4512015745624783</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5640819040847384</v>
+        <v>0.4512012438260519</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5640816100968039</v>
+        <v>0.4512009498381175</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4512010233351011</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5640812426118855</v>
+        <v>0.4512005823531992</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.56408113236641</v>
+        <v>0.4512004721077236</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5640810956179183</v>
+        <v>0.4512004353592319</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5640812426118855</v>
+        <v>0.4512005823531992</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5640807648814919</v>
+        <v>0.4512001046228055</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5640817203422792</v>
+        <v>0.4512010600835928</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5640816835937875</v>
+        <v>0.4512010233351011</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5640813528573611</v>
+        <v>0.4512006925986747</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.564081793839263</v>
+        <v>0.4512011335805766</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5640811691149019</v>
+        <v>0.4512005088562155</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5640809853724428</v>
+        <v>0.4512003251137564</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5640805811390327</v>
+        <v>0.4511999208803463</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5640797359237207</v>
+        <v>0.4511990756650344</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.564079699175229</v>
+        <v>0.4511990389165427</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5640798461691963</v>
+        <v>0.4511991859105099</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5640797726722127</v>
+        <v>0.4511991124135263</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5640798461691963</v>
+        <v>0.4511991859105099</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4521789472830329</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5640798829176882</v>
+        <v>0.4511992226590018</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5640797726722127</v>
+        <v>0.4511991124135263</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5640802136541146</v>
+        <v>0.4511995533954282</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5640801034086391</v>
+        <v>0.4511994431499527</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5640800666601472</v>
+        <v>0.4511994064014608</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5640799931631636</v>
+        <v>0.4511993329044771</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5640799564146719</v>
+        <v>0.4511992961559854</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5640797359237207</v>
+        <v>0.4511990756650344</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5640796624267371</v>
+        <v>0.4511990021680508</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5640795889297535</v>
+        <v>0.4511989286710671</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5640796256782454</v>
+        <v>0.4511989654195591</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5640795154327699</v>
+        <v>0.4511988551740835</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5640796256782454</v>
+        <v>0.4511989654195591</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5640799196661799</v>
+        <v>0.4511992594074935</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000008.xlsx
+++ b/out/MLP_Base_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4511417746543884</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5955144575003584</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5028553605079651</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5796381235122681</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.946808764566225</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.6008297204971313</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.946808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5334447026252747</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4765050709247589</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4672377407550812</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4298610091209412</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4464905858039856</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4271084368228912</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4455704987049103</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4339965283870697</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.433061808347702</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4273340702056885</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4892988502979279</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4379752278327942</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4072205722332001</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4062727689743042</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4071820676326752</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4024487435817719</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3940680921077728</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4019909799098969</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3958730697631836</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.421121746301651</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4045464992523193</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3983241617679596</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3913942873477936</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3973371684551239</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4068676829338074</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4253277778625488</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.5542242527008057</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4515193998813629</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4437921941280365</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4362329542636871</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4145614504814148</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4434157311916351</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4082862138748169</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4053031206130981</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4648251235485077</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4801957607269287</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4732755124568939</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5281159281730652</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5944738984107971</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5840041041374207</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001268986134462757</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1457821337244151</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4962825179100037</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.179279226522314</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5594884753227234</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4644436240196228</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4875524938106537</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4562403857707977</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4526073336601257</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4484370946884155</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4916861355304718</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4686508178710938</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4827284514904022</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4728397130966187</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.475258857011795</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5036421418190002</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1459090323378613</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5637801885604858</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1460198482380828</v>
+        <v>-0.1413152098439792</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3984684831700167</v>
+        <v>0.3866971705496043</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4841989278793335</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.179279226522314</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6516827066599384</v>
+        <v>0.6328216039830502</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02839079576504601</v>
+        <v>0.02755209221229843</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5220987796783447</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.179279226522314</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3093561868546149</v>
+        <v>0.3006083131520255</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04978778242834846</v>
+        <v>0.04831698216083748</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5557315945625305</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3805316650209108</v>
+        <v>0.3696809904884391</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06048658754653359</v>
+        <v>0.05869942713510714</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4871628880500793</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4517120636879264</v>
+        <v>0.4387582652113344</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01600626656819838</v>
+        <v>0.01553333914567821</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4414096772670746</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4231607839207831</v>
+        <v>0.4110505727412286</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00889165984094642</v>
+        <v>0.008628612207711016</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6047221422195435</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4249232363480751</v>
+        <v>0.4127608036328733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01868350094727638</v>
+        <v>0.01813185613580216</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5771306753158569</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4534093974891268</v>
+        <v>0.440405888840853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007336528310594483</v>
+        <v>0.007119746131842187</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5490150451660156</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4493843578343242</v>
+        <v>0.4364995439891501</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005223278394710401</v>
+        <v>0.005069759167679973</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4660261273384094</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.179279226522314</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4524918418123275</v>
+        <v>0.43951513596091</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002053563057449922</v>
+        <v>0.00199245795350187</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.503171980381012</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4513698941943718</v>
+        <v>0.4384263431205321</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001163391180593178</v>
+        <v>0.00112793867775196</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4487207233905792</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4516419139573071</v>
+        <v>0.4386901410130672</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004400859384283726</v>
+        <v>0.0004271678768908736</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.44631427526474</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4513577606188883</v>
+        <v>0.4384140897504338</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002030815238056566</v>
+        <v>0.0001975767215885757</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4173516631126404</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4513246228372562</v>
+        <v>0.438381767907178</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.169590296362756e-05</v>
+        <v>6.927392708056564e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4415557980537415</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4512636566847388</v>
+        <v>0.4383225691068454</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.741833032797311e-05</v>
+        <v>1.69413445763141e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4594649076461792</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4512272017260541</v>
+        <v>0.4382871071020824</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4486746191978455</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4512221838546451</v>
+        <v>0.4382820899753154</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4679358899593353</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4512180563535662</v>
+        <v>0.4382779265144847</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4087210893630981</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4512152552076886</v>
+        <v>0.438275125368607</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4273901879787445</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4512098114626822</v>
+        <v>0.4382696816236006</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4450467228889465</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4512038187292519</v>
+        <v>0.4382636888901703</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4601993560791016</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4511984509406735</v>
+        <v>0.4382583211015919</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4703633785247803</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4511984876891652</v>
+        <v>0.4382583578500836</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4633984863758087</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4511985979346407</v>
+        <v>0.4382584680955592</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4407484233379364</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4511986714316243</v>
+        <v>0.4382585415925428</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4941581189632416</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4511988551740835</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5599943399429321</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.45120039861074</v>
+        <v>0.4382602687716584</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3477187752723694</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4512018685504131</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.2973871827125549</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.451203117999135</v>
+        <v>0.4382629881600535</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8930670022964478</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.179279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4512044776933324</v>
+        <v>0.4382643478542508</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5888631939888</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.946808764566225</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4512022727838231</v>
+        <v>0.4382621429447415</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.65186607837677</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.946808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4512018685504131</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.596734881401062</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.179279226522314</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4512010233351011</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4930660724639893</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4512015745624783</v>
+        <v>0.4382614447233968</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.458029568195343</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4512012438260519</v>
+        <v>0.4382611139869704</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.4837292432785034</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4512009498381175</v>
+        <v>0.4382608199990359</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4571909010410309</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4512010233351011</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.435324639081955</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4512005823531992</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4289804100990295</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4512004721077236</v>
+        <v>0.438260342268642</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.443262130022049</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4512004353592319</v>
+        <v>0.4382603055201503</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4318557679653168</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4512005823531992</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.624781608581543</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.179279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4512001046228055</v>
+        <v>0.4382599747837239</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6664077639579773</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.179279226522314</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4512010600835928</v>
+        <v>0.4382609302445112</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4940507411956787</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4512010233351011</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4760806560516357</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4512006925986747</v>
+        <v>0.4382605627595931</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.440833568572998</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4512011335805766</v>
+        <v>0.4382610037414951</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4467703700065613</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4512005088562155</v>
+        <v>0.4382603790171339</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4547730982303619</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4512003251137564</v>
+        <v>0.4382601952746748</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4627688825130463</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4511999208803463</v>
+        <v>0.4382597910412648</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4763141274452209</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4511990756650344</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4736945629119873</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4511990389165427</v>
+        <v>0.4382589090774611</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4732994437217712</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4511991859105099</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4549053907394409</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4511991124135263</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5561697483062744</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4511991859105099</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4512230753898621</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.179279226522314</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4511992226590018</v>
+        <v>0.4382590928199203</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5202199816703796</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4511991124135263</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4291022717952728</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4117496884784029</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4511995533954282</v>
+        <v>0.4382594235563467</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4473420381546021</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4511994431499527</v>
+        <v>0.4382593133108711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4080899059772491</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4511994064014608</v>
+        <v>0.4382592765623792</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4284122288227081</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4511993329044771</v>
+        <v>0.4382592030653956</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4181913137435913</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4511992961559854</v>
+        <v>0.4382591663169039</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4093296229839325</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4511990756650344</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4480581879615784</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4511990021680508</v>
+        <v>0.4382588723289692</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4297841489315033</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4511989286710671</v>
+        <v>0.4382587988319855</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4226986169815063</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4511989654195591</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4580549299716949</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4511988551740835</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5144959092140198</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.179279226522314</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4511989654195591</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.501798689365387</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.946808764566225</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4511992594074935</v>
+        <v>0.438259129568412</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000008.xlsx
+++ b/out/MLP_Base_repeat_5_000008.xlsx
@@ -72494,7 +72494,7 @@
         <v>0.65186607837677</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4382617387113315</v>
@@ -73289,7 +73289,7 @@
         <v>0.596734881401062</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4382608934960195</v>
@@ -74084,7 +74084,7 @@
         <v>0.4930660724639893</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4382614447233968</v>
@@ -74879,7 +74879,7 @@
         <v>0.458029568195343</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4382611139869704</v>
@@ -75674,7 +75674,7 @@
         <v>0.4837292432785034</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.4382608199990359</v>
@@ -76469,7 +76469,7 @@
         <v>0.4571909010410309</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0.4382608934960195</v>
@@ -77264,7 +77264,7 @@
         <v>0.435324639081955</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0.4382604525141176</v>
@@ -80444,7 +80444,7 @@
         <v>0.624781608581543</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
         <v>0.4382599747837239</v>
@@ -81239,7 +81239,7 @@
         <v>0.6664077639579773</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0.4382609302445112</v>
@@ -82034,7 +82034,7 @@
         <v>0.4940507411956787</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0.4382608934960195</v>
@@ -82829,7 +82829,7 @@
         <v>0.4760806560516357</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0.4382605627595931</v>
@@ -83624,7 +83624,7 @@
         <v>0.440833568572998</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0.4382610037414951</v>
@@ -89189,7 +89189,7 @@
         <v>0.4549053907394409</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.4382589825744447</v>
